--- a/zeus-pipetter/calibration_for_pipetting/pipetting_calibration_substances_ALL.xlsx
+++ b/zeus-pipetter/calibration_for_pipetting/pipetting_calibration_substances_ALL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chemiluminescence\OneDrive\roborea\zeus-pipetter\calibration_for_pipetting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB9073B-0DE0-4E19-A93A-0A63F203BFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B287B4-339E-4369-B17E-47177E599CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{6AD12529-BA13-4E6D-84B7-065B2794C4B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{6AD12529-BA13-4E6D-84B7-065B2794C4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Solvents" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>reaction_id</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>DMF_50ul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 4 5 8 10 20 30 50 </t>
   </si>
   <si>
     <t>DMF_1000ul</t>
@@ -455,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -485,7 +482,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
         <v>0.5</v>
@@ -509,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -533,7 +530,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
@@ -557,7 +554,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
@@ -581,7 +578,7 @@
         <v>75</v>
       </c>
       <c r="F6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1">
         <v>10</v>
@@ -605,7 +602,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
         <v>20</v>
@@ -687,9 +684,7 @@
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" ht="18.75">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
